--- a/artfynd/A 26090-2025 artfynd.xlsx
+++ b/artfynd/A 26090-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127298861</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26090-2025 artfynd.xlsx
+++ b/artfynd/A 26090-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298867</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127298861</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26090-2025 artfynd.xlsx
+++ b/artfynd/A 26090-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298867</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127298861</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26090-2025 artfynd.xlsx
+++ b/artfynd/A 26090-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298867</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127298861</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26090-2025 artfynd.xlsx
+++ b/artfynd/A 26090-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298867</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127298861</v>
       </c>
       <c r="B3" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
